--- a/data/JTL_Rechnungstexte.xlsx
+++ b/data/JTL_Rechnungstexte.xlsx
@@ -780,7 +780,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 7 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
@@ -850,7 +850,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 14 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
@@ -920,7 +920,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 21 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
@@ -1127,7 +1127,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 7 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
@@ -1197,7 +1197,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 14 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
@@ -1267,7 +1267,7 @@
 -	Transport insurance for the net value of the goods is included
 -	ADSp 2017 apply in their current version (https://www.dslv.org/de/adsp)
 Deviations from the above information, lack of availability of a contact person or lack of access at the time of delivery may result in additional cost, which you will be responsible for.
-Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 1 TAG]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
+Your goods are scheduled for packaging on [KOMMISSIONIERUNGSTERMIN], and will be handed over to the carrier on [KOMMISSIONIERUNGSTERMIN + 2 TAGE]. If you need a fixed delivery date, please contact us by sending an email to info@elvinci.de.
 You have a payment term of 21 days, which starts from the day the goods are made available for pickup. Please be advised that we reduce your payment term by 7 days for each invoice which is not paid in time.
 TIP: Since October 2025, real-time transfers throughout Europe cost the same as normal SEPA transfers. In many other countries outside Europe, this cost adjustment has also already been implemented or there is at least a transition schedule. If possible, please make your transfer a real-time transfer to ensure that you do not exceed the latest payment date.</t>
         </is>
